--- a/data/UNSPED_Karbon_Veri_Girisi_v3.xlsx
+++ b/data/UNSPED_Karbon_Veri_Girisi_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andrey\Desktop\carbon_project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CF4E14-8E3D-4214-88CC-E11E6CA68332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8903EC8-13F7-44FB-9DC5-47B440A9A018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
     <author>UNSPED Importer</author>
   </authors>
   <commentList>
-    <comment ref="E4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -77,7 +77,115 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="358">
+  <si>
+    <t>UNSPED — KARBON AYAK İZİ VERİ GİRİŞ ŞABLONU v3</t>
+  </si>
+  <si>
+    <t>NASIL KULLANILIR</t>
+  </si>
+  <si>
+    <t>1.  Alt sekmelerde her emisyon kategorisi için ilgili sayfayı açın.</t>
+  </si>
+  <si>
+    <t>2.  MAVİ hücreleri doldurun. YEŞİL hücreler online'dan otomatik dolar — gerekirse üzerine yazın.</t>
+  </si>
+  <si>
+    <t>3.  GRİ hücrelere dokunmayın — sistem hesaplar.</t>
+  </si>
+  <si>
+    <t>4.  Dosyayı kaydedin ve importer'ı çalıştırın:   python pipeline/importer.py</t>
+  </si>
+  <si>
+    <t>5.  Sistem bu dosyayı okur, DB'den + online'dan emisyon faktörlerini çeker,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    CO2e hesaplayıp sonuçları otomatik kaydeder.</t>
+  </si>
+  <si>
+    <t>RENK KODLARI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  🔵 MAVİ     — Siz doldurursunuz (aktivite verisi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  🟢 YEŞİL    — Online'dan otomatik dolar, üzerine yazabilirsiniz (emisyon faktörleri)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ⚪ GRİ      — Hesaplanan, dokunmayın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  🟡 SARI     — Toplamlar</t>
+  </si>
+  <si>
+    <t>SAYFALAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1.1_Stationary        — Sabit yakma (doğalgaz, motorin, benzin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1.2_Mobile            — Hareketli yakma (şirket araçları)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1.4_Refrigerants      — Soğutucu gazlar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2.1_Electricity       — Elektrik tüketimi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3.1_Freight           — Hammadde sevkiyatı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3.2_ProductShipment   — Ürün sevkiyatı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3.3_Commuting         — Personel işe gidiş gelişleri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3.4_BusinessTravel    — İş seyahati karayolu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3.5_FlightsHotels     — Uçak &amp; konaklama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  4.1_Purchased         — Satın alınan malzemeler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  4.2_Capital           — Sermaye varlıkları</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  4.3_Waste             — Atık bertarafı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  4.4_LeasedEquipment   — Kiralanan ekipmanlar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  4.5_Services          — Hizmet alımları</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  6.1_TDLosses          — İletim &amp; dağıtım kayıpları</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  PERSONNEL             — Lokasyon &amp; personel sayısı ← SİZ GİRİN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  TOTAL_EMISSIONS       — Tüm kapsamlar özet toplam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  IMPACT_ANALYSIS       — %95 etkili emisyon kaynakları</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  PER_CAPITA            — Lokasyon başına ton CO2e / kişi</t>
+  </si>
+  <si>
+    <t>ÖNEMLİ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Sütun eklemeyin/silmeyin. Sekme adlarını değiştirmeyin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Veri tablolarının altına satır ekleyebilirsiniz.</t>
+  </si>
   <si>
     <t>1.1 — Sabit Yakma Kaynaklı Emisyonlar</t>
   </si>
@@ -202,114 +310,6 @@
     <t>← TOTALS (yellow)</t>
   </si>
   <si>
-    <t>UNSPED — KARBON AYAK İZİ VERİ GİRİŞ ŞABLONU v3</t>
-  </si>
-  <si>
-    <t>NASIL KULLANILIR</t>
-  </si>
-  <si>
-    <t>1.  Alt sekmelerde her emisyon kategorisi için ilgili sayfayı açın.</t>
-  </si>
-  <si>
-    <t>2.  MAVİ hücreleri doldurun. YEŞİL hücreler online'dan otomatik dolar — gerekirse üzerine yazın.</t>
-  </si>
-  <si>
-    <t>3.  GRİ hücrelere dokunmayın — sistem hesaplar.</t>
-  </si>
-  <si>
-    <t>4.  Dosyayı kaydedin ve importer'ı çalıştırın:   python pipeline/importer.py</t>
-  </si>
-  <si>
-    <t>5.  Sistem bu dosyayı okur, DB'den + online'dan emisyon faktörlerini çeker,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    CO2e hesaplayıp sonuçları otomatik kaydeder.</t>
-  </si>
-  <si>
-    <t>RENK KODLARI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  🔵 MAVİ     — Siz doldurursunuz (aktivite verisi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  🟢 YEŞİL    — Online'dan otomatik dolar, üzerine yazabilirsiniz (emisyon faktörleri)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ⚪ GRİ      — Hesaplanan, dokunmayın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  🟡 SARI     — Toplamlar</t>
-  </si>
-  <si>
-    <t>SAYFALAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  1.1_Stationary        — Sabit yakma (doğalgaz, motorin, benzin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  1.2_Mobile            — Hareketli yakma (şirket araçları)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  1.4_Refrigerants      — Soğutucu gazlar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  2.1_Electricity       — Elektrik tüketimi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3.1_Freight           — Hammadde sevkiyatı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3.2_ProductShipment   — Ürün sevkiyatı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3.3_Commuting         — Personel işe gidiş gelişleri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3.4_BusinessTravel    — İş seyahati karayolu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3.5_FlightsHotels     — Uçak &amp; konaklama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4.1_Purchased         — Satın alınan malzemeler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4.2_Capital           — Sermaye varlıkları</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4.3_Waste             — Atık bertarafı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4.4_LeasedEquipment   — Kiralanan ekipmanlar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4.5_Services          — Hizmet alımları</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  6.1_TDLosses          — İletim &amp; dağıtım kayıpları</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  PERSONNEL             — Lokasyon &amp; personel sayısı ← SİZ GİRİN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  TOTAL_EMISSIONS       — Tüm kapsamlar özet toplam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  IMPACT_ANALYSIS       — %95 etkili emisyon kaynakları</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  PER_CAPITA            — Lokasyon başına ton CO2e / kişi</t>
-  </si>
-  <si>
-    <t>ÖNEMLİ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Sütun eklemeyin/silmeyin. Sekme adlarını değiştirmeyin.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Veri tablolarının altına satır ekleyebilirsiniz.</t>
-  </si>
-  <si>
     <t>1.2 — Hareketli Yakma — Şirket Araçları</t>
   </si>
   <si>
@@ -320,12 +320,6 @@
   </si>
   <si>
     <t>Dizel araçlar</t>
-  </si>
-  <si>
-    <t>• YEŞİL hücreler otomatik güncellenir, üzerine yazılabilir.</t>
-  </si>
-  <si>
-    <t>• Yakıt türü: petrol (L) | diesel (L)</t>
   </si>
   <si>
     <t>• Kaynak: IPCC 2006 REF#3 &amp; REF#5</t>
@@ -411,7 +405,12 @@
     <t>2.1 — Elektrik Tüketimi (Kapsam 2)</t>
   </si>
   <si>
-    <t>Tüketim (kWh)</t>
+    <t>Tüketim
+(kWh/MWh/GWh)</t>
+  </si>
+  <si>
+    <t>Birim
+🟢 Değiştirilebilir</t>
   </si>
   <si>
     <t>EF
@@ -422,6 +421,9 @@
     <t>EF Kaynak</t>
   </si>
   <si>
+    <t>kWh</t>
+  </si>
+  <si>
     <t>TEİAŞ/EPDK REF#10</t>
   </si>
   <si>
@@ -449,7 +451,8 @@
     <t>Araç Tipi</t>
   </si>
   <si>
-    <t>Mesafe (km)</t>
+    <t>Mesafe
+(km/mil/m)</t>
   </si>
   <si>
     <t>EF
@@ -467,6 +470,9 @@
   </si>
   <si>
     <t>All HGVs</t>
+  </si>
+  <si>
+    <t>km</t>
   </si>
   <si>
     <t>3.1.2</t>
@@ -1199,7 +1205,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1325,8 +1331,19 @@
       <color rgb="FF00008B"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF375623"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1423,8 +1440,18 @@
         <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1516,11 +1543,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1592,24 +1656,17 @@
     <xf numFmtId="0" fontId="13" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1619,14 +1676,49 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1938,244 +2030,244 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="30"/>
+      <c r="A1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="30"/>
+      <c r="A3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="33"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="30"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="33"/>
     </row>
     <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="30"/>
+      <c r="A5" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="33"/>
     </row>
     <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="30"/>
+      <c r="A6" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="33"/>
     </row>
     <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="30"/>
+      <c r="A7" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="33"/>
     </row>
     <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="30"/>
+      <c r="A8" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="33"/>
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="30"/>
+      <c r="A9" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="33"/>
     </row>
     <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="30"/>
+      <c r="A10" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="33"/>
     </row>
     <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="36"/>
-      <c r="B11" s="30"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="33"/>
     </row>
     <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="30"/>
+      <c r="A12" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="33"/>
     </row>
     <row r="13" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="36"/>
-      <c r="B13" s="30"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="33"/>
     </row>
     <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="30"/>
+      <c r="A14" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="33"/>
     </row>
     <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="30"/>
+      <c r="A15" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="33"/>
     </row>
     <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="30"/>
+      <c r="A16" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="33"/>
     </row>
     <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="30"/>
+      <c r="A17" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="33"/>
     </row>
     <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="36"/>
-      <c r="B18" s="30"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="33"/>
     </row>
     <row r="19" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="30"/>
+      <c r="A19" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="33"/>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="36"/>
-      <c r="B20" s="30"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="33"/>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="30"/>
+      <c r="A21" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="33"/>
     </row>
     <row r="22" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="30"/>
+      <c r="A22" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="33"/>
     </row>
     <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="30"/>
+      <c r="A23" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="33"/>
     </row>
     <row r="24" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="30"/>
+      <c r="A24" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="33"/>
     </row>
     <row r="25" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="30"/>
+      <c r="A25" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="33"/>
     </row>
     <row r="26" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="30"/>
+      <c r="A26" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="33"/>
     </row>
     <row r="27" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="30"/>
+      <c r="A27" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="33"/>
     </row>
     <row r="28" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" s="30"/>
+      <c r="A28" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="33"/>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="30"/>
+      <c r="A29" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="33"/>
     </row>
     <row r="30" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="30"/>
+      <c r="A30" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="33"/>
     </row>
     <row r="31" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="30"/>
+      <c r="A31" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="33"/>
     </row>
     <row r="32" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" s="30"/>
+      <c r="A32" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="33"/>
     </row>
     <row r="33" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="30"/>
+      <c r="A33" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="33"/>
     </row>
     <row r="34" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" s="30"/>
+      <c r="A34" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" s="33"/>
     </row>
     <row r="35" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="B35" s="30"/>
+      <c r="A35" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="33"/>
     </row>
     <row r="36" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="B36" s="30"/>
+      <c r="A36" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="33"/>
     </row>
     <row r="37" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="B37" s="30"/>
+      <c r="A37" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="33"/>
     </row>
     <row r="38" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="B38" s="30"/>
+      <c r="A38" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="33"/>
     </row>
     <row r="39" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" s="30"/>
+      <c r="A39" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="33"/>
     </row>
     <row r="40" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="36"/>
-      <c r="B40" s="30"/>
+      <c r="A40" s="32"/>
+      <c r="B40" s="33"/>
     </row>
     <row r="41" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="B41" s="30"/>
+      <c r="A41" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" s="33"/>
     </row>
     <row r="42" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="B42" s="30"/>
+      <c r="A42" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B42" s="33"/>
     </row>
     <row r="43" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="B43" s="30"/>
+      <c r="A43" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="42">
@@ -2243,58 +2335,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="A1" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
+      <c r="A2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2302,10 +2394,10 @@
         <v>2025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -2330,10 +2422,10 @@
         <v>2025</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
@@ -2358,10 +2450,10 @@
         <v>2025</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -2380,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2388,10 +2480,10 @@
         <v>2025</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
@@ -2410,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2418,10 +2510,10 @@
         <v>2025</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
@@ -2440,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2488,79 +2580,79 @@
       <c r="I12" s="2"/>
     </row>
     <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="34"/>
+      <c r="A14" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="41"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
+      <c r="A15" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
+      <c r="A16" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
+      <c r="A17" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
     </row>
     <row r="19" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="6" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
       <c r="B21" s="10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2592,58 +2684,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="A1" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
+      <c r="A2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2651,22 +2743,22 @@
         <v>2025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H4" s="19">
         <v>0</v>
@@ -2678,22 +2770,22 @@
         <v>2025</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H5" s="19">
         <v>0</v>
@@ -2705,22 +2797,22 @@
         <v>2025</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="H6" s="19">
         <v>0</v>
@@ -2732,22 +2824,22 @@
         <v>2025</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H7" s="19">
         <v>0</v>
@@ -2759,22 +2851,22 @@
         <v>2025</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F8" s="4">
         <v>0</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H8" s="19">
         <v>0</v>
@@ -2826,66 +2918,66 @@
       <c r="I12" s="2"/>
     </row>
     <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="34"/>
+      <c r="A14" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="41"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
+      <c r="A15" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
+      <c r="A16" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
     </row>
     <row r="18" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="6" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
       <c r="B20" s="10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2917,58 +3009,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="A1" s="42" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
+      <c r="A2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2976,16 +3068,16 @@
         <v>2025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -2994,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I4" s="19">
         <v>0</v>
@@ -3005,16 +3097,16 @@
         <v>2025</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
@@ -3023,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I5" s="19">
         <v>0</v>
@@ -3034,16 +3126,16 @@
         <v>2025</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
@@ -3052,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I6" s="19">
         <v>0</v>
@@ -3063,16 +3155,16 @@
         <v>2025</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
@@ -3081,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I7" s="19">
         <v>0</v>
@@ -3132,66 +3224,66 @@
       <c r="I11" s="3"/>
     </row>
     <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="34"/>
+      <c r="A13" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="41"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
+      <c r="A14" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
+      <c r="A15" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
     </row>
     <row r="17" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="6" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9"/>
       <c r="B19" s="10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
       <c r="B20" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3223,58 +3315,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="A1" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
+      <c r="A2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3282,22 +3374,22 @@
         <v>2025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H4" s="19">
         <v>0</v>
@@ -3309,22 +3401,22 @@
         <v>2025</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>215</v>
       </c>
       <c r="H5" s="19">
         <v>0</v>
@@ -3336,22 +3428,22 @@
         <v>2025</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F6" s="4">
         <v>0</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H6" s="19">
         <v>0</v>
@@ -3363,22 +3455,22 @@
         <v>2025</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H7" s="19">
         <v>0</v>
@@ -3390,22 +3482,22 @@
         <v>2025</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F8" s="4">
         <v>0</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H8" s="19">
         <v>0</v>
@@ -3457,66 +3549,66 @@
       <c r="I12" s="2"/>
     </row>
     <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="34"/>
+      <c r="A14" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="41"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
+      <c r="A15" s="37" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
+      <c r="A16" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
     </row>
     <row r="18" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="6" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
       <c r="B20" s="10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3548,58 +3640,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>226</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="A1" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
+      <c r="A2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3607,22 +3699,22 @@
         <v>2025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H4" s="19">
         <v>0</v>
@@ -3634,20 +3726,20 @@
         <v>2025</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H5" s="19">
         <v>0</v>
@@ -3699,66 +3791,66 @@
       <c r="I9" s="2"/>
     </row>
     <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="34"/>
+      <c r="A11" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="41"/>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
-        <v>231</v>
-      </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
+      <c r="A12" s="37" t="s">
+        <v>232</v>
+      </c>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
+      <c r="A13" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
     </row>
     <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3790,58 +3882,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>232</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="A1" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
+      <c r="A2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3849,22 +3941,22 @@
         <v>2025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H4" s="19">
         <v>0</v>
@@ -3876,22 +3968,22 @@
         <v>2025</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H5" s="19">
         <v>0</v>
@@ -3903,22 +3995,22 @@
         <v>2025</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F6" s="4">
         <v>0</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H6" s="19">
         <v>0</v>
@@ -3930,22 +4022,22 @@
         <v>2025</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H7" s="19">
         <v>0</v>
@@ -3957,22 +4049,22 @@
         <v>2025</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F8" s="4">
         <v>0</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H8" s="19">
         <v>0</v>
@@ -4024,66 +4116,66 @@
       <c r="I12" s="2"/>
     </row>
     <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="34"/>
+      <c r="A14" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="41"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
-        <v>231</v>
-      </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
+      <c r="A15" s="37" t="s">
+        <v>232</v>
+      </c>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
+      <c r="A16" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
     </row>
     <row r="18" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="6" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
       <c r="B20" s="10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -4100,48 +4192,48 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="20" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>244</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-    </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-    </row>
-    <row r="3" spans="1:7" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
+        <v>245</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+    </row>
+    <row r="3" spans="1:8" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>245</v>
+        <v>38</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>246</v>
@@ -4150,151 +4242,161 @@
         <v>247</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>84</v>
+        <v>248</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2025</v>
       </c>
       <c r="B4" s="2">
         <v>1416240</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="4">
         <v>0.434</v>
       </c>
-      <c r="D4" s="4">
+      <c r="E4" s="4">
         <v>0.47799999999999998</v>
       </c>
-      <c r="E4" s="3">
+      <c r="F4" s="3" t="e">
         <f>D4-C4</f>
-        <v>4.3999999999999984E-2</v>
-      </c>
-      <c r="F4" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G4" s="19">
         <v>62.314599999999999</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H4" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2024</v>
       </c>
       <c r="B5" s="2">
         <v>1027730</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="4">
         <v>0.442</v>
       </c>
-      <c r="D5" s="4">
+      <c r="E5" s="4">
         <v>0.47799999999999998</v>
       </c>
-      <c r="E5" s="3">
+      <c r="F5" s="3" t="e">
         <f>D5-C5</f>
-        <v>3.5999999999999976E-2</v>
-      </c>
-      <c r="F5" s="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G5" s="19">
         <v>36.9983</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="3"/>
+      <c r="E6" s="4"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G6" s="3"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="3"/>
+      <c r="E7" s="4"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G7" s="3"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="3"/>
+      <c r="E8" s="4"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G8" s="3"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="3"/>
+      <c r="E9" s="4"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="33"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="40"/>
       <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="34"/>
-    </row>
-    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-    </row>
-    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="29"/>
+    </row>
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="37" t="s">
         <v>250</v>
       </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-    </row>
-    <row r="15" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+    </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -4322,38 +4424,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
+      <c r="A1" s="42" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>252</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
+      <c r="A2" s="38" t="s">
+        <v>253</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
     </row>
     <row r="3" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4361,16 +4463,16 @@
         <v>2024</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C4" s="2">
         <v>250</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4378,16 +4480,16 @@
         <v>2024</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C5" s="2">
         <v>380</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4395,16 +4497,16 @@
         <v>2024</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C6" s="2">
         <v>90</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4412,16 +4514,16 @@
         <v>2024</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C7" s="2">
         <v>54</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4481,72 +4583,72 @@
       <c r="E15" s="2"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="32" t="s">
-        <v>267</v>
-      </c>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="34"/>
+      <c r="A17" s="39" t="s">
+        <v>268</v>
+      </c>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="41"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
+      <c r="A18" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
-        <v>269</v>
-      </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
+      <c r="A19" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="29" t="s">
-        <v>270</v>
-      </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
+      <c r="A20" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
+      <c r="A21" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
     </row>
     <row r="23" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="6" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
       <c r="B25" s="10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4554,16 +4656,16 @@
         <v>2025</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C27" s="23">
         <v>250</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4571,16 +4673,16 @@
         <v>2025</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C28" s="23">
         <v>380</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4588,16 +4690,16 @@
         <v>2025</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C29" s="23">
         <v>90</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4605,16 +4707,16 @@
         <v>2025</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C30" s="23">
         <v>54</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -4644,51 +4746,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="A1" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="A2" s="38" t="s">
+        <v>274</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
     </row>
     <row r="3" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -4697,10 +4799,10 @@
     </row>
     <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
@@ -4710,15 +4812,15 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C6" s="19">
         <v>0</v>
@@ -4728,15 +4830,15 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -4746,15 +4848,15 @@
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C8" s="20">
         <v>0</v>
@@ -4775,10 +4877,10 @@
     </row>
     <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
@@ -4787,10 +4889,10 @@
     </row>
     <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C11" s="19">
         <v>0</v>
@@ -4800,15 +4902,15 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C12" s="20">
         <v>0</v>
@@ -4829,10 +4931,10 @@
     </row>
     <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
@@ -4841,7 +4943,7 @@
     </row>
     <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>120</v>
@@ -4854,15 +4956,15 @@
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
@@ -4872,15 +4974,15 @@
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -4890,15 +4992,15 @@
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -4908,15 +5010,15 @@
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C19" s="19">
         <v>0</v>
@@ -4926,15 +5028,15 @@
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
@@ -4944,15 +5046,15 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C21" s="19">
         <v>0</v>
@@ -4962,15 +5064,15 @@
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C22" s="19">
         <v>0</v>
@@ -4980,15 +5082,15 @@
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C23" s="19">
         <v>0</v>
@@ -4998,15 +5100,15 @@
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C24" s="19">
         <v>0</v>
@@ -5016,15 +5118,15 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C25" s="19">
         <v>36.9983</v>
@@ -5034,15 +5136,15 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C26" s="20">
         <v>37</v>
@@ -5063,10 +5165,10 @@
     </row>
     <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C28" s="20">
         <v>37</v>
@@ -5080,25 +5182,25 @@
     <row r="31" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7"/>
       <c r="B32" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
       <c r="B33" s="10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -5125,48 +5227,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>337</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="A1" s="42" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>338</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="A2" s="38" t="s">
+        <v>339</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:7" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5174,13 +5276,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E4" s="21">
         <v>664.21659999999997</v>
@@ -5197,13 +5299,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E5" s="21">
         <v>627.89089999999999</v>
@@ -5220,13 +5322,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E6" s="19">
         <v>492.34789999999998</v>
@@ -5243,13 +5345,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E7" s="19">
         <v>62.314599999999999</v>
@@ -5266,13 +5368,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E8" s="19">
         <v>27.622699999999998</v>
@@ -5285,15 +5387,15 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
-        <v>347</v>
-      </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="34"/>
+      <c r="A9" s="44" t="s">
+        <v>348</v>
+      </c>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="41"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="22"/>
@@ -5314,58 +5416,58 @@
       <c r="G11" s="22"/>
     </row>
     <row r="12" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="42"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="34"/>
+      <c r="A12" s="45"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="41"/>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="40"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
+      <c r="A13" s="43"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="40"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
+      <c r="A14" s="43"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="40"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="40"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
+      <c r="A16" s="43"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="40"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
+      <c r="A17" s="43"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="22"/>
@@ -5547,7 +5649,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -5564,100 +5666,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
+      <c r="A1" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
+      <c r="A2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
     </row>
     <row r="3" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2">
-        <v>9835</v>
+        <v>11064</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F4" s="4">
         <v>48</v>
@@ -5678,30 +5780,30 @@
         <v>273</v>
       </c>
       <c r="L4" s="4">
-        <v>7.1699999999999997E-4</v>
+        <v>7.2000000000000005E-4</v>
       </c>
       <c r="M4" s="19">
         <v>19.048500000000001</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2">
-        <v>3200</v>
+        <v>432</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="F5" s="4">
         <v>43</v>
@@ -5722,30 +5824,30 @@
         <v>273</v>
       </c>
       <c r="L5" s="4">
-        <v>8.3199999999999995E-4</v>
+        <v>8.4500000000000005E-4</v>
       </c>
       <c r="M5" s="19">
         <v>8.5360999999999994</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="D6" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="F6" s="4">
         <v>43</v>
@@ -5766,30 +5868,30 @@
         <v>273</v>
       </c>
       <c r="L6" s="4">
-        <v>8.3199999999999995E-4</v>
+        <v>8.4500000000000005E-4</v>
       </c>
       <c r="M6" s="19">
         <v>2.6700000000000002E-2</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D7" s="2">
         <v>5</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="F7" s="4">
         <v>44.3</v>
@@ -5810,13 +5912,13 @@
         <v>273</v>
       </c>
       <c r="L7" s="4">
-        <v>7.45E-4</v>
+        <v>7.7499999999999997E-4</v>
       </c>
       <c r="M7" s="19">
         <v>1.15E-2</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5836,176 +5938,496 @@
       <c r="N8" s="2"/>
     </row>
     <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
+      <c r="A9" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="2">
+        <v>8294</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="4">
+        <v>48</v>
+      </c>
+      <c r="G9" s="4">
+        <v>56.1</v>
+      </c>
+      <c r="H9" s="4">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="J9" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="K9" s="4">
+        <v>273</v>
+      </c>
+      <c r="L9" s="4">
+        <v>7.2000000000000005E-4</v>
+      </c>
       <c r="M9" s="3"/>
-      <c r="N9" s="2"/>
+      <c r="N9" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
+      <c r="A10" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1366</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="4">
+        <v>43</v>
+      </c>
+      <c r="G10" s="4">
+        <v>74.099999999999994</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="I10" s="4">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="J10" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="K10" s="4">
+        <v>273</v>
+      </c>
+      <c r="L10" s="4">
+        <v>8.4500000000000005E-4</v>
+      </c>
       <c r="M10" s="3"/>
-      <c r="N10" s="2"/>
+      <c r="N10" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="2"/>
+      <c r="A11" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="4">
+        <v>43</v>
+      </c>
+      <c r="G11" s="4">
+        <v>74.099999999999994</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="I11" s="4">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="J11" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="K11" s="4">
+        <v>273</v>
+      </c>
+      <c r="L11" s="4">
+        <v>8.4500000000000005E-4</v>
+      </c>
+      <c r="M11" s="47"/>
+      <c r="N11" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="4">
+        <v>44.3</v>
+      </c>
+      <c r="G12" s="4">
+        <v>69.3</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="I12" s="4">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="J12" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="K12" s="4">
+        <v>273</v>
+      </c>
+      <c r="L12" s="4">
+        <v>7.7499999999999997E-4</v>
+      </c>
+      <c r="M12" s="47"/>
+      <c r="N12" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="34"/>
-    </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-    </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-    </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-    </row>
-    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-    </row>
-    <row r="19" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-      <c r="B20" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9"/>
-      <c r="B21" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12" t="s">
-        <v>35</v>
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="47"/>
+      <c r="N13" s="46"/>
+    </row>
+    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="2">
+        <v>9835</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="4">
+        <v>48</v>
+      </c>
+      <c r="G14" s="4">
+        <v>56.1</v>
+      </c>
+      <c r="H14" s="4">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="J14" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="K14" s="4">
+        <v>273</v>
+      </c>
+      <c r="L14" s="4">
+        <v>7.2000000000000005E-4</v>
+      </c>
+      <c r="M14" s="47"/>
+      <c r="N14" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="2">
+        <v>3200</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="4">
+        <v>43</v>
+      </c>
+      <c r="G15" s="4">
+        <v>74.099999999999994</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="I15" s="4">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="J15" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="K15" s="4">
+        <v>273</v>
+      </c>
+      <c r="L15" s="4">
+        <v>8.4500000000000005E-4</v>
+      </c>
+      <c r="M15" s="47"/>
+      <c r="N15" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="2">
+        <v>10</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="4">
+        <v>43</v>
+      </c>
+      <c r="G16" s="4">
+        <v>74.099999999999994</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="I16" s="4">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="J16" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="K16" s="4">
+        <v>273</v>
+      </c>
+      <c r="L16" s="4">
+        <v>8.4500000000000005E-4</v>
+      </c>
+      <c r="M16" s="47"/>
+      <c r="N16" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="2">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="4">
+        <v>44.3</v>
+      </c>
+      <c r="G17" s="4">
+        <v>69.3</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="I17" s="4">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="J17" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="K17" s="4">
+        <v>273</v>
+      </c>
+      <c r="L17" s="4">
+        <v>7.7499999999999997E-4</v>
+      </c>
+      <c r="M17" s="47"/>
+      <c r="N17" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="2"/>
+    </row>
+    <row r="20" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="41"/>
+    </row>
+    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+    </row>
+    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+    </row>
+    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="33"/>
+    </row>
+    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+    </row>
+    <row r="26" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7"/>
+      <c r="B27" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="9"/>
+      <c r="B28" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="11"/>
+      <c r="B29" s="12" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A17:N17"/>
+    <mergeCell ref="A24:N24"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A16:N16"/>
-    <mergeCell ref="A15:N15"/>
-    <mergeCell ref="A13:N13"/>
-    <mergeCell ref="A14:N14"/>
+    <mergeCell ref="A23:N23"/>
+    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="A20:N20"/>
+    <mergeCell ref="A21:N21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6025,51 +6447,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>348</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="A1" s="42" t="s">
+        <v>349</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>349</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="A2" s="38" t="s">
+        <v>350</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6077,7 +6499,7 @@
         <v>2024</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C4" s="23">
         <v>250</v>
@@ -6103,7 +6525,7 @@
         <v>2024</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C5" s="23">
         <v>380</v>
@@ -6129,7 +6551,7 @@
         <v>2024</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C6" s="23">
         <v>90</v>
@@ -6155,7 +6577,7 @@
         <v>2024</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C7" s="23">
         <v>54</v>
@@ -6181,7 +6603,7 @@
         <v>2024</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C8" s="20">
         <v>774</v>
@@ -6223,54 +6645,54 @@
       <c r="H10" s="22"/>
     </row>
     <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="42"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="34"/>
+      <c r="A11" s="45"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="40"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
+      <c r="A12" s="43"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="40"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
+      <c r="A13" s="43"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="40"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
+      <c r="A14" s="43"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="40"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="22"/>
@@ -6555,100 +6977,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
+      <c r="A2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
     </row>
     <row r="3" spans="1:14" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D4" s="2">
-        <v>123248.19</v>
+        <v>87312.66</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="F4" s="4">
         <v>44.3</v>
@@ -6657,10 +7079,10 @@
         <v>69.3</v>
       </c>
       <c r="H4" s="4">
-        <v>0.01</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I4" s="4">
-        <v>6.0000000000000002E-5</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="J4" s="4">
         <v>29.8</v>
@@ -6669,7 +7091,7 @@
         <v>273</v>
       </c>
       <c r="L4" s="4">
-        <v>7.45E-4</v>
+        <v>7.7499999999999997E-4</v>
       </c>
       <c r="M4" s="19">
         <v>283.16500000000002</v>
@@ -6680,19 +7102,19 @@
     </row>
     <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2">
-        <v>78573.77</v>
+        <v>122850.92</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="F5" s="4">
         <v>43</v>
@@ -6701,10 +7123,10 @@
         <v>74.099999999999994</v>
       </c>
       <c r="H5" s="4">
-        <v>0.01</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="I5" s="4">
-        <v>6.0000000000000002E-5</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="J5" s="4">
         <v>29.8</v>
@@ -6713,7 +7135,7 @@
         <v>273</v>
       </c>
       <c r="L5" s="4">
-        <v>8.3199999999999995E-4</v>
+        <v>8.4500000000000005E-4</v>
       </c>
       <c r="M5" s="19">
         <v>209.18289999999999</v>
@@ -6739,36 +7161,88 @@
       <c r="N6" s="2"/>
     </row>
     <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
+      <c r="A7" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="2">
+        <v>139533.07999999999</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="4">
+        <v>44.3</v>
+      </c>
+      <c r="G7" s="4">
+        <v>69.3</v>
+      </c>
+      <c r="H7" s="4">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I7" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="J7" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="K7" s="4">
+        <v>273</v>
+      </c>
+      <c r="L7" s="4">
+        <v>7.7499999999999997E-4</v>
+      </c>
       <c r="M7" s="3"/>
-      <c r="N7" s="2"/>
+      <c r="N7" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
+      <c r="A8" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="2">
+        <v>72875.179999999993</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="4">
+        <v>43</v>
+      </c>
+      <c r="G8" s="4">
+        <v>74.099999999999994</v>
+      </c>
+      <c r="H8" s="4">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="I8" s="4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J8" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="K8" s="4">
+        <v>273</v>
+      </c>
+      <c r="L8" s="4">
+        <v>8.4500000000000005E-4</v>
+      </c>
       <c r="M8" s="3"/>
-      <c r="N8" s="2"/>
+      <c r="N8" s="2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
@@ -6786,110 +7260,182 @@
       <c r="M9" s="3"/>
       <c r="N9" s="2"/>
     </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="2">
+        <v>151020.57999999999</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="4">
+        <v>44.3</v>
+      </c>
+      <c r="G10" s="4">
+        <v>69.3</v>
+      </c>
+      <c r="H10" s="4">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I10" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="J10" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="K10" s="4">
+        <v>273</v>
+      </c>
+      <c r="L10" s="4">
+        <v>7.7499999999999997E-4</v>
+      </c>
+      <c r="M10" s="3"/>
+      <c r="N10" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
     <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="34"/>
+      <c r="A11" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="2">
+        <v>78573.77</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="4">
+        <v>43</v>
+      </c>
+      <c r="G11" s="4">
+        <v>74.099999999999994</v>
+      </c>
+      <c r="H11" s="4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="I11" s="4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J11" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="K11" s="4">
+        <v>273</v>
+      </c>
+      <c r="L11" s="4">
+        <v>8.4500000000000005E-4</v>
+      </c>
+      <c r="M11" s="3"/>
+      <c r="N11" s="2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="2"/>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="2"/>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="2"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="2"/>
     </row>
     <row r="16" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="6" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="2">
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A12:N12"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="A13:N13"/>
-    <mergeCell ref="A14:N14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6897,7 +7443,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -6909,246 +7455,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="A1" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="A2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:7" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2">
-        <v>0.46</v>
+        <v>226.25</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="18">
-        <v>1526</v>
-      </c>
-      <c r="F4" s="19">
-        <v>0.70199999999999996</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>87</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.04</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" s="18">
-        <v>4</v>
-      </c>
-      <c r="F5" s="19">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>89</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="2">
-        <v>202.5</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" s="18">
-        <v>2088</v>
-      </c>
-      <c r="F6" s="19">
-        <v>422.82</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1.25</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" s="18">
-        <v>771</v>
-      </c>
-      <c r="F7" s="19">
-        <v>0.9637</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" s="18">
-        <v>1774</v>
-      </c>
-      <c r="F8" s="19">
-        <v>13.305</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>95</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="2">
-        <v>12</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="18">
-        <v>8060</v>
-      </c>
-      <c r="F9" s="19">
-        <v>96.72</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>97</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" s="2">
-        <v>29</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" s="18">
-        <v>3220</v>
-      </c>
-      <c r="F10" s="19">
-        <v>93.38</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>97</v>
-      </c>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="2">
-        <v>128</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E11" s="18">
-        <v>3220</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4"/>
       <c r="F11" s="3"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="2">
-        <v>92</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E12" s="18">
-        <v>1</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="4"/>
       <c r="F12" s="3"/>
       <c r="G12" s="2"/>
     </row>
@@ -7170,82 +7606,371 @@
       <c r="F14" s="3"/>
       <c r="G14" s="2"/>
     </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="2"/>
+    </row>
     <row r="16" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="34"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="18">
+        <v>1526</v>
+      </c>
+      <c r="F25" s="19">
+        <v>0.70199999999999996</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="18">
+        <v>4</v>
+      </c>
+      <c r="F26" s="19">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="2">
+        <v>202.5</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E27" s="18">
+        <v>2088</v>
+      </c>
+      <c r="F27" s="19">
+        <v>422.82</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="18">
+        <v>771</v>
+      </c>
+      <c r="F28" s="19">
+        <v>0.9637</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="18">
+        <v>1774</v>
+      </c>
+      <c r="F29" s="19">
+        <v>13.305</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="2">
+        <v>12</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E30" s="18">
+        <v>8060</v>
+      </c>
+      <c r="F30" s="19">
+        <v>96.72</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="2">
+        <v>29</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="18">
+        <v>3220</v>
+      </c>
+      <c r="F31" s="19">
+        <v>93.38</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="2">
+        <v>128</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" s="18">
+        <v>3220</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="2">
+        <v>92</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="18">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="2"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="51"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="52"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="33"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-    </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-    </row>
-    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="B22" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9"/>
-      <c r="B23" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12" t="s">
-        <v>35</v>
+      <c r="B39" s="33"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="33"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="5"/>
+      <c r="B41" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="7"/>
+      <c r="B42" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="9"/>
+      <c r="B43" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="11"/>
+      <c r="B44" s="12" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7253,178 +7978,199 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="3" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+    </row>
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+    </row>
+    <row r="3" spans="1:7" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-    </row>
-    <row r="3" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2025</v>
       </c>
       <c r="B4" s="2">
         <v>1416240</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="4">
         <v>0.46899999999999997</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="19">
+      <c r="F4" s="19">
         <v>664.21659999999997</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="4"/>
+      <c r="C5" s="31" t="s">
+        <v>107</v>
+      </c>
       <c r="D5" s="4"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E5" s="4"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="4"/>
+      <c r="C6" s="31" t="s">
+        <v>107</v>
+      </c>
       <c r="D6" s="4"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E6" s="4"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="4"/>
+      <c r="C7" s="31" t="s">
+        <v>107</v>
+      </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="4"/>
+      <c r="C8" s="31" t="s">
+        <v>107</v>
+      </c>
       <c r="D8" s="4"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="4"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="4"/>
+      <c r="C9" s="31" t="s">
+        <v>107</v>
+      </c>
       <c r="D9" s="4"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="33"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="40"/>
       <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="34"/>
-    </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="29"/>
+    </row>
+    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+    </row>
+    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-    </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+    </row>
+    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-    </row>
-    <row r="16" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="6" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -7443,7 +8189,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -7451,47 +8197,45 @@
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="6" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:10" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-    </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-    </row>
-    <row r="3" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+    </row>
+    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+    </row>
+    <row r="3" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>115</v>
@@ -7499,20 +8243,23 @@
       <c r="E3" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23">
         <v>2025</v>
       </c>
@@ -7531,146 +8278,165 @@
       <c r="F4" s="2">
         <v>0</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="H4" s="17">
         <v>8.2229999999999998E-2</v>
       </c>
-      <c r="H4" s="19">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I4" s="19">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
         <v>2025</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="H5" s="18">
         <v>0.14843999999999999</v>
       </c>
-      <c r="H5" s="19">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I5" s="19">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G6" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G7" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G8" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
+      <c r="G9" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
       <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="34"/>
-    </row>
-    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-    </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="29"/>
+    </row>
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+    </row>
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -7687,7 +8453,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -7695,47 +8461,45 @@
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="6" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-    </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-    </row>
-    <row r="3" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+    </row>
+    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+    </row>
+    <row r="3" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>115</v>
@@ -7743,28 +8507,31 @@
       <c r="E3" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23">
         <v>2025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>121</v>
@@ -7775,146 +8542,153 @@
       <c r="F4" s="2">
         <v>0</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="H4" s="17">
         <v>8.2229999999999998E-2</v>
       </c>
-      <c r="H4" s="19">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I4" s="19">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
         <v>2025</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="H5" s="18">
         <v>0.14843999999999999</v>
       </c>
-      <c r="H5" s="19">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I5" s="19">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H6" s="4"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="4"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H8" s="4"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
       <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="34"/>
-    </row>
-    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-    </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="29"/>
+    </row>
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+    </row>
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -7949,88 +8723,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
+      <c r="A1" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
+      <c r="A2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
     </row>
     <row r="3" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="O3" s="1" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8038,19 +8812,19 @@
         <v>2025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G4" s="4">
         <v>44.3</v>
@@ -8083,19 +8857,19 @@
         <v>2025</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G5" s="4">
         <v>43</v>
@@ -8128,19 +8902,19 @@
         <v>2025</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G6" s="4">
         <v>43</v>
@@ -8237,84 +9011,84 @@
       <c r="O10" s="2"/>
     </row>
     <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="34"/>
+      <c r="A12" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="41"/>
     </row>
     <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="30"/>
+      <c r="A13" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33"/>
     </row>
     <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
+      <c r="A14" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
     </row>
     <row r="16" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="6" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -8331,7 +9105,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -8339,47 +9113,45 @@
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="6" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-    </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-    </row>
-    <row r="3" spans="1:9" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+    </row>
+    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+    </row>
+    <row r="3" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>115</v>
@@ -8387,178 +9159,188 @@
       <c r="E3" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23">
         <v>2025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="H4" s="18">
         <v>0.14843999999999999</v>
       </c>
-      <c r="H4" s="19">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I4" s="19">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
         <v>2025</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="H5" s="18">
         <v>0.14843999999999999</v>
       </c>
-      <c r="H5" s="19">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I5" s="19">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H6" s="4"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="4"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H8" s="4"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
       <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="34"/>
-    </row>
-    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-    </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="29"/>
+    </row>
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+    </row>
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
